--- a/docs/deliverables/01_요구사항정의서_비드체크.xlsx
+++ b/docs/deliverables/01_요구사항정의서_비드체크.xlsx
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104건 기준 핵심 요건 192 / 198, 틀린 충족·미충족 0</t>
+          <t>104건 기준 핵심 요건 191 / 198, 틀린 충족·미충족 0 (2026-10-15)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">

--- a/docs/deliverables/01_요구사항정의서_비드체크.xlsx
+++ b/docs/deliverables/01_요구사항정의서_비드체크.xlsx
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104건 기준 핵심 요건 191 / 198, 틀린 충족·미충족 0 (2026-10-15)</t>
+          <t>104건 기준 핵심 요건 192 / 198, 틀린 충족·미충족 0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">

--- a/docs/deliverables/01_요구사항정의서_비드체크.xlsx
+++ b/docs/deliverables/01_요구사항정의서_비드체크.xlsx
@@ -470,16 +470,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -522,17 +522,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>회원</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>계정</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>아이디 로그인</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>아이디·비밀번호로 로그인하고 HttpOnly 세션 쿠키를 발급</t>
+          <t>아이디·비밀번호로 로그인하고 세션 쿠키를 발급한다</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>로그인 실패 횟수 제한·잠금</t>
+          <t>로그인 실패 횟수 제한</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -559,17 +559,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>회원</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>계정</t>
+          <t>계정 관리</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>회원가입</t>
+          <t>관리자 계정 발급</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>아이디·비밀번호만으로 가입하고 바로 로그인</t>
+          <t>관리자가 계정을 만든다. 회사 없이 만든 계정은 첫 로그인 때 회사 프로필을 직접 만든다</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>회사 없는 무료 요금제 사용자로 생성, 설정(AUTH_SIGNUP_ENABLED)으로 끌 수 있음</t>
+          <t>만든 계정이 그 회사의 관리자</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -596,17 +596,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>회원</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>계정</t>
+          <t>권한</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>계정 발급</t>
+          <t>회사별 접근 격리</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -616,34 +616,34 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>관리자가 회사 소속 계정을 만든다</t>
+          <t>회사가 다른 계정의 검토 건·프로필에 접근할 수 없다</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>회사 관리자는 일반 사용자만 추가</t>
+          <t>회사별 격리</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · 보안</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>회원</t>
+          <t>계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>세션 관리</t>
+          <t>회원가입</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>자체 회원가입</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>세션을 폐기하고 쿠키를 지운다</t>
+          <t>누구나 아이디·비밀번호로 가입하고 바로 로그인한다. 가입한 계정은 회사 없는 무료 요금제 사용자다</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>세션 토큰은 해시로만 저장</t>
+          <t>설정으로 끌 수 있음</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -670,69 +670,69 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>회원</t>
+          <t>공고</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>권한</t>
+          <t>수집</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>회사별 격리</t>
+          <t>공고 · 변경 차수 수집</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AUTH-005</t>
+          <t>NOTI-001</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>다른 회사의 검토 건·프로필·판정에 접근할 수 없다</t>
+          <t>나라장터 공고와 변경 차수를 주기적으로 수집하고 차수별로 저장한다</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>403 COMPANY_ACCESS_DENIED</t>
+          <t>용역 · 물품 · 공사 · 외자</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MVP · 보안</t>
+          <t>MVP · 나라장터 Open API</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>회원</t>
+          <t>공고</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>권한</t>
+          <t>첨부</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>운영 관리</t>
+          <t>첨부 본문 추출</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>AUTH-006</t>
+          <t>NOTI-002</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>시스템 관리자만 운영 관리 화면과 작업 API를 쓴다</t>
+          <t>첨부 문서를 내려받아 PDF · HWP · HWPX에서 글자를 추출한다</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>일반 계정에는 메뉴가 보이지 않음</t>
+          <t>겹쳐 그린 글자 사본 제거</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>검색</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>공고·차수 수집</t>
+          <t>공고 검색 · 상태 필터</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NOTI-001</t>
+          <t>NOTI-003</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>나라장터 입찰공고와 변경 차수를 주기적으로 수집해 차수별로 저장</t>
+          <t>공고번호 · 공고명 · 기관으로 검색하고 판정 상태로 거른다</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>용역·물품·공사·외자, 변경·재공고·취소 포함</t>
+          <t>띄어쓰기 무시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>MVP · 나라장터 Open API</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>
@@ -786,27 +786,27 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>원문</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>과거 이력 보충</t>
+          <t>나라장터 원문 연결</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>NOTI-002</t>
+          <t>NOTI-004</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>뒤늦게 발견한 공고의 과거 차수를 보충 수집</t>
+          <t>판정 화면에서 그 공고의 나라장터 상세로 바로 간다</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>실패 시 되돌리기·재시도</t>
+          <t>나라장터 주소만</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -818,106 +818,106 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>공고</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>첨부</t>
+          <t>요건 추출</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>문서 내려받기</t>
+          <t>자격 요건 구조화</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NOTI-003</t>
+          <t>QUAL-001</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>첨부 문서를 내려받아 S3에 보관</t>
+          <t>공고문에서 참가자격 요건을 유형 · 연산 · 값 · 근거 문장으로 구조화한다</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>같은 문서 중복 제거, 지원하지 않는 형식은 분석 대상에서 제외</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MVP · AWS S3</t>
+          <t>MVP · OpenAI API</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>공고</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>첨부</t>
+          <t>근거 확인</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>본문 추출</t>
+          <t>인용 문장 대조</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>NOTI-004</t>
+          <t>QUAL-002</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>PDF·HWP·HWPX에서 글자와 표를 추출</t>
+          <t>요건의 인용 문장이 저장된 공고문에 있는지 확인하고, 없으면 판정하지 않는다</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>겹쳐 그린 글자 사본 제거, 암호화 PDF 처리</t>
+          <t>문서 해시 대조</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · 핵심 원칙</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>공고</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>공고 찾기</t>
+          <t>규칙 판정</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NOTI-005</t>
+          <t>QUAL-003</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>공고번호·공고명·기관명으로 검색하고 판정 상태·사업 유형으로 거른다</t>
+          <t>요건과 회사 프로필을 규칙으로 비교해 충족 · 미충족 · 확인 필요로 판정한다</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>띄어쓰기 무시, 서버 쪽 쪽 넘김</t>
+          <t>결정론적</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -929,32 +929,32 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>공고</t>
+          <t>판정</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>검색</t>
+          <t>종합 판정</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>원문 연결</t>
+          <t>핵심 자격 종합 판정</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>NOTI-006</t>
+          <t>QUAL-004</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>판정 화면에서 그 공고의 나라장터 상세로 바로 간다</t>
+          <t>핵심 자격만으로 종합 판정을 내고, 이름으로 적힌 조건은 "확인할 항목"으로 분리한다</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>나라장터 주소만 연결</t>
+          <t>핵심 요건 충족 · 미충족 · 확인 필요</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -971,32 +971,32 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>요건 추출</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>자격 요건 구조화</t>
+          <t>확인 필요 질문 · 재판정</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>QUAL-001</t>
+          <t>QUAL-005</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>공고문에서 참가자격 요건을 유형·연산·값·근거 문장으로 구조화</t>
+          <t>회사 정보가 없어 판정하지 못한 항목을 사용자에게 묻고, 답하면 그 줄만 다시 판정한다</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>청크 경계에서 생긴 가짜 요건 차단</t>
+          <t>확인 필요 화면</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>MVP · OpenAI API</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>
@@ -1008,103 +1008,95 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>요건 추출</t>
+          <t>근거 원문</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>면허제한 대조</t>
+          <t>판정 · 원문 나란히 보기</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>QUAL-002</t>
+          <t>QUAL-006</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>나라장터 면허제한·참가가능지역 정보를 요건과 대조</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>업종 코드 풀이, 포함 면허</t>
-        </is>
-      </c>
+          <t>판정과 공고문을 나란히 보여 주고 요건이 나온 문장을 표시한다</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>MVP · 나라장터 Open API</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>근거 확인</t>
+          <t>비교</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>인용 대조</t>
+          <t>차수 비교</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>QUAL-003</t>
+          <t>CHG-001</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>요건의 인용 문장이 저장된 공고문에 있는지 확인하고 없으면 판정하지 않는다</t>
+          <t>차수 사이의 공고 값(마감 · 금액 · 계약방법)과 자격 요건의 변화를 비교한다</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>문서 해시 대조</t>
+          <t>화면 맨 위에 요약</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>MVP · 핵심 원칙</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>재검증</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>규칙 비교</t>
+          <t>영향 요건 재판정</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>QUAL-004</t>
+          <t>CHG-002</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>요건과 회사 프로필을 결정론적 규칙으로 비교해 충족·미충족·확인 필요로 판정</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>약한 근거는 미충족으로 확정하지 않음</t>
-        </is>
-      </c>
+          <t>변경으로 영향받은 요건만 다시 판정한다</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
@@ -1114,32 +1106,32 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>프로필</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>기본 정보</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>종합 판정</t>
+          <t>회사 프로필 관리</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>QUAL-005</t>
+          <t>PROF-001</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>업종·소재지·기업 구분·품명번호 같은 닫힌 값의 핵심 자격으로만 종합 판정</t>
+          <t>업종 · 소재지 · 기업 구분 · 인력 · 실적 · 인증을 관리하고 한 번에 저장한다</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>이름으로 적힌 조건은 확인할 항목으로 분리</t>
+          <t>저장 전 표시</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1151,69 +1143,69 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>프로필</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>조달청 조회</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>질문과 재판정</t>
+          <t>사업자등록번호 조회</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>QUAL-006</t>
+          <t>PROF-002</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>회사 정보가 없어 판정하지 못한 항목을 묻고 답하면 그 줄만 다시 판정</t>
+          <t>사업자등록번호로 조달청 등록 정보를 불러와 프로필에 채운다</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>확인 필요 화면</t>
+          <t>업종은 더하기만</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · 조달청 API</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>프로필</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>근거 원문</t>
+          <t>자동 재판정</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>나란히 보기</t>
+          <t>저장 후 자동 재판정</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>QUAL-007</t>
+          <t>PROF-003</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>판정과 공고문을 나란히 놓고 요건이 나온 문장을 표시</t>
+          <t>프로필을 저장하면 마지막으로 보던 공고를 다시 판정한다</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>PDF·HWP 원문 보기</t>
+          <t>모델 호출 없음</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1225,30 +1217,34 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>프로필</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>평가 대응</t>
+          <t>초기화</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>평가 항목 확인</t>
+          <t>프로필 초기화</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>QUAL-008</t>
+          <t>PROF-004</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>제안서 평가 항목과 공고문 내 위치를 보여 준다</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
+          <t>실적 · 인증 · 인력 · 사업자등록번호를 비운다</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>필수 값은 유지</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
@@ -1258,106 +1254,106 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>Copilot</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>비교</t>
+          <t>공고별 대화</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>차수 비교</t>
+          <t>공고문 근거 답변</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CHG-001</t>
+          <t>COP-001</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>차수 사이의 공고 값(마감·금액·계약방법)과 자격 요건의 변화를 비교</t>
+          <t>판정 결과와 공고문 발췌를 근거로 질문에 답하고 근거를 함께 보여 준다</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>판정 화면 맨 위에 요약</t>
+          <t>근거 없으면 답하지 않음</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · OpenAI API</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>Copilot</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>재검증</t>
+          <t>일반 도우미</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>영향 요건 재판정</t>
+          <t>사이트 · 입찰 안내</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>CHG-002</t>
+          <t>COP-002</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>변경으로 영향받은 요건만 다시 판정</t>
+          <t>사이트 사용법과 입찰 일반 지식에 답한다</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>변경이 없으면 기존 분석 재사용</t>
+          <t>회사 정보는 전달하지 않음</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · OpenAI API</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>Copilot</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>기본 정보</t>
+          <t>공고 찾기</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>회사 프로필</t>
+          <t>공고 찾기 연결</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PROF-001</t>
+          <t>COP-003</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>업종·소재지·기업 구분·인력·실적·인증을 관리하고 한 번에 저장</t>
+          <t>"…공고 찾아줘"라고 하면 공고를 찾아 판정 화면으로 이어 준다</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>저장 전에는 화면에만 반영</t>
+          <t>모델 호출 없음</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1369,34 +1365,30 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>Copilot</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>기본 정보</t>
+          <t>추천 공고 판정</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>업종 검색</t>
+          <t>추천 공고 판정 연결</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>PROF-002</t>
+          <t>COP-004</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>업종명·코드로 검색해 여러 개를 고른다</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>6개 표시 후 더보기로 펼침</t>
-        </is>
-      </c>
+          <t>"AI 추천 공고 판정해줘"라고 하면 추천 공고를 판정 화면으로 이어 준다</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
@@ -1406,71 +1398,67 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>Copilot</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>조달청 조회</t>
+          <t>대화 기록</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>사업자번호로 채우기</t>
+          <t>계정별 대화 보관</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>PROF-003</t>
+          <t>COP-005</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>사업자등록번호로 조달청 등록 정보(회사명·소재지·업종)를 불러와 채운다</t>
+          <t>대화 기록을 계정마다 따로 보관한다</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>업종은 더하기만</t>
+          <t>브라우저 저장</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>MVP · 조달청 API</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>자동 재판정</t>
+          <t>AI 추천</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>저장 후 재판정</t>
+          <t>연관 공고 추천</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>PROF-004</t>
+          <t>REC-001</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>프로필을 저장하면 마지막으로 보던 공고를 다시 판정</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>모델 호출 없음</t>
-        </is>
-      </c>
+          <t>회사와 연관성이 높은 공고를 순위로 보여 주고 판정과 분리해 표시한다</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
           <t>MVP</t>
@@ -1480,108 +1468,104 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>요금제</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>초기화</t>
+          <t>한도</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>프로필 초기화</t>
+          <t>사용량 집계</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PROF-005</t>
+          <t>PLAN-001</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>실적·인증·인력·사업자등록번호를 비운다</t>
+          <t>요금제별로 참가자격 확인 수와 Copilot 질문 수를 계정마다 센다</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>필수 값은 유지, 확인 후 실행</t>
+          <t>무료 3건 · 6회 · 10회</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · BM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>내 입찰</t>
+          <t>요금제</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>검토 건</t>
+          <t>멤버십</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>카드 목록</t>
+          <t>멤버십 창</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CASE-001</t>
+          <t>PLAN-002</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>검토 중인 공고를 카드로 보여 주고 마감일·변경 여부를 표시</t>
+          <t>한도를 넘으면 멤버십 창을 띄우고 같은 창에서 가입으로 이어진다</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>3×3 쪽 넘김</t>
+          <t>실제 결제 없음</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>MVP</t>
+          <t>MVP · BM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>내 입찰</t>
+          <t>요금제</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>검토 건</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>찾기·정렬</t>
+          <t>남은 횟수 표시</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CASE-002</t>
+          <t>PLAN-003</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>검토 건 안에서 찾고 최근·오래된·마감 가까운·공고명 순으로 정렬</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>마감 지난 공고는 뒤로</t>
-        </is>
-      </c>
+          <t>남은 질문 수와 이번 달 확인 수를 화면에 보여 준다</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>MVP</t>
@@ -1596,27 +1580,27 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>만료</t>
+          <t>검토 건</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>만료 표시·삭제</t>
+          <t>검토 건 카드</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>CASE-003</t>
+          <t>CASE-001</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>마감이 지난 공고에 만료됨을 표시하고 지울 수 있게 한다</t>
+          <t>검토 중인 공고를 카드로 보여 주고 마감일을 표시한다</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>마감 전 공고는 삭제 거절(409)</t>
+          <t>3×3 쪽 넘김</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -1633,27 +1617,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>화면 복귀</t>
+          <t>만료</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>보던 화면 기억</t>
+          <t>만료 표시 · 삭제</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CASE-004</t>
+          <t>CASE-002</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>다른 탭에 다녀와도 보던 공고 또는 목록으로 돌아온다</t>
+          <t>마감이 지난 공고에 "만료됨"을 표시하고 지울 수 있게 한다</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>브라우저 탭 단위 기억</t>
+          <t>마감 전은 삭제 거절</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1665,143 +1649,143 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Copilot</t>
+          <t>내 입찰</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>공고별 대화</t>
+          <t>찾기 · 정렬</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>근거 답변</t>
+          <t>검토 건 찾기 · 정렬</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>COP-001</t>
+          <t>CASE-003</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>판정 결과와 공고문 발췌를 근거로 질문에 답하고 근거를 보여 준다</t>
+          <t>검토 건 안에서 찾고, 최근 · 오래된 · 마감 가까운 · 공고명 순으로 정렬한다</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>근거 없으면 답하지 않음</t>
+          <t>마감 지난 공고는 뒤로</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>MVP · OpenAI API</t>
+          <t>MVP</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Copilot</t>
+          <t>지침서</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>공고별 대화</t>
+          <t>생성</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Django 중계</t>
+          <t>입찰 준비 지침서 생성</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>COP-002</t>
+          <t>GUIDE-001</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>동의한 공고문 질문을 Django가 받아 로그인 확인 후 FastAPI로 넘기고 요청 기록을 남긴다</t>
+          <t>판정을 마친 공고의 평가 항목 · 제출 서류 · 일정 · 준비 순서를 정리한다</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>질문 원문은 저장하지 않음(길이·해시만)</t>
+          <t>공고 질문 1회 사용</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>MVP · Django</t>
+          <t>MVP · OpenAI API</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Copilot</t>
+          <t>지침서</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>일반 도우미</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>사이트 안내</t>
+          <t>인용 · 프로필 대조</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>COP-003</t>
+          <t>GUIDE-002</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>사이트 사용법과 입찰 일반 지식에 답한다</t>
+          <t>공고에서 뽑은 항목은 인용문이 문서에 있을 때만 남기고, 준비물은 회사 프로필 항목만 가리킨다</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>회사 정보는 전달하지 않음</t>
+          <t>회사 사실을 지어내지 않음</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>MVP · OpenAI API</t>
+          <t>MVP · 핵심 원칙</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Copilot</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>일반 도우미</t>
+          <t>관리</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>공고 찾기 연결</t>
+          <t>작업 관리</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>COP-004</t>
+          <t>ADMIN-001</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>"…공고 찾아줘"라고 하면 공고를 찾아 판정 화면으로 이어 준다</t>
+          <t>시스템 관리자가 수집 · 처리 작업을 관리한다</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>모델 호출 없음</t>
+          <t>관리자 전용</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1811,496 +1795,23 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Copilot</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>일반 도우미</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>추천 공고 판정</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>COP-005</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>"AI 추천 공고 판정해줘"라고 하면 추천 공고를 판정 화면으로 이어 준다</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>모델 호출 없음</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Copilot</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>대화 기록</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>계정별 보관</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>COP-006</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>대화 기록을 계정마다 따로 보관한다</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>브라우저 저장</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Copilot</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>동의</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>외부 전달 안내</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>COP-007</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>처음 질문할 때 회사 정보가 외부 API로 전달될 수 있다는 안내에 동의받는다</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>동의 전 질문 불가</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>MVP · 법적 요건</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>지침서</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>생성</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>입찰 준비 지침서</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>GUIDE-001</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>판정을 마친 공고의 평가 항목·배점, 제출 서류, 일정, 준비 순서를 정리한다</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>한 번에 그 공고의 Copilot 질문 1회 사용</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>MVP · OpenAI API</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>지침서</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>인용·프로필 대조</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>GUIDE-002</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>공고에서 뽑은 항목은 인용문이 문서에 있을 때만 남기고, 준비물은 회사 프로필 항목만 가리킨다</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>회사 사실을 지어내지 않음</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>MVP · 핵심 원칙</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>지침서</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>표시</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>준비물 상태</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>GUIDE-003</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>준비물마다 프로필에 있음 / 준비 필요를 표시하고 제출 서류 체크리스트를 제공한다</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>결과는 브라우저에 보관</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>AI 추천</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>연관 공고 추천</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>REC-001</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>회사와 연관성이 높은 공고를 순위로 보여 주고 판정과 분리해 표시</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>BM25 개인화 추천</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>AI 추천</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>판정 연결</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>REC-002</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>추천 공고에서 판정 화면으로 바로 간다</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>요금제</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>한도</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>사용량 집계</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-001</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>요금제별로 참가자격 확인 수와 Copilot 질문 수를 계정마다 센다</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>무료 월 3건·공고당 6회·일반 도우미 월 10회, 베이직 월 20건·합산 50회</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>MVP · BM</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>요금제</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>멤버십</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>멤버십 창</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>PLAN-002</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>한도를 넘으면 멤버십 창을 띄우고 같은 창에서 가입으로 이어진다</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>실제 결제 없음, 카드 정보 미수집</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>요금제</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>표시</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>남은 횟수</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-003</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>남은 질문 수와 이번 달 확인 수를 화면에 보여 준다</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>관리</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>작업 관리</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>ADMIN-001</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>시스템 관리자가 수집·처리 작업과 관련성 라벨을 관리한다</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>관리자 전용</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>배포</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>자동 배포</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>OPS-001</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>develop 병합 후 CI가 통과하면 AWS에 자동 배포한다</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>스키마 검사 실패 시 이전 버전으로 복귀</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>MVP · GitHub Actions</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>총 기능 요구사항 건수: 48건</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>v1.0 (2026-10-14)</t>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>총 기능 요구사항 건수: 35건</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>v1.1 (2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -2315,7 +1826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2376,7 +1887,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>근거가 부족한 요건을 충족·미충족으로 확정하지 않는다</t>
+          <t>틀린 확정 판정을 내지 않는다</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2408,12 +1919,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>판정 규칙을 바꿔도 기대값 일치가 기준선 아래로 내려가지 않는다</t>
+          <t>판정 규칙 변경이 정확도를 떨어뜨리지 않는다</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>골든 회귀 기대값 일치 ≥ 105 / 138 (CI 게이트)</t>
+          <t>기대값 일치가 기준선(105) 아래로 내려가지 않음</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2425,27 +1936,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>정확성</t>
+          <t>신뢰성</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NFR-A-003</t>
+          <t>NFR-R-001</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>실제 공고 표본 정확도</t>
+          <t>판정 근거 표시</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>정답을 붙인 실제 공고에서 핵심 요건을 맞힌다</t>
+          <t>모든 판정에 근거 문장과 문서 위치를 붙인다</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104건 기준 핵심 요건 192 / 198, 틀린 충족·미충족 0</t>
+          <t>근거 없는 요건은 "확인 필요"</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2462,22 +1973,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>NFR-R-001</t>
+          <t>NFR-R-002</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>판정 근거 표시</t>
+          <t>지침서 근거 확인</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>모든 판정에 근거 문장과 문서 위치를 붙인다</t>
+          <t>지침서는 문서에 없는 항목과 프로필에 없는 회사 사실을 내보내지 않는다</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>근거 없는 요건은 확인 필요</t>
+          <t>인용 대조 · 프로필 항목 id 대조</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2489,27 +2000,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>신뢰성</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NFR-R-002</t>
+          <t>NFR-S-001</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>생성 내용 근거 확인</t>
+          <t>회사 간 데이터 격리</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>지침서는 문서에 없는 항목과 프로필에 없는 회사 사실을 내보내지 않는다</t>
+          <t>회사 간 데이터를 격리한다</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>인용문 대조 · 프로필 항목 id 대조</t>
+          <t>다른 회사의 검토 건 접근 시 403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2521,59 +2032,59 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>신뢰성</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>NFR-R-003</t>
+          <t>NFR-S-002</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>제품 경로와 엔진 일치</t>
+          <t>비밀 정보 관리</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>화면에서 판정한 결과가 엔진 회귀 결과와 같다</t>
+          <t>비밀 값을 저장소와 이미지에 두지 않는다</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>골든 계정 32개 요건 104 / 104 일치</t>
+          <t>AWS SSM에서 실행 시 주입</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>NFR-P-001</t>
+          <t>NFR-S-003</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>일반 API 응답 시간</t>
+          <t>결제 정보 미수집</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>공고 검색·상세·검토 건·업종 검색 응답 시간</t>
+          <t>결제 정보를 받거나 저장하지 않는다</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>로컬 측정 중앙값 &lt; 100ms</t>
+          <t>가입 API에 카드 필드 없음</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2585,27 +2096,27 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>NFR-P-002</t>
+          <t>NFR-O-001</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>재판정 응답 시간</t>
+          <t>스키마 정합 배포</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>저장된 분석으로 다시 판정하는 시간(모델 호출 없음)</t>
+          <t>DB 스키마와 코드가 어긋나면 배포하지 않는다</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>&lt; 500ms</t>
+          <t>스키마 검사 실패 시 이전 버전으로 복귀</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2617,724 +2128,116 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>NFR-P-003</t>
+          <t>NFR-O-002</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Copilot 답변 시간</t>
+          <t>자동 배포</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>일반 도우미 모델 답변 시간</t>
+          <t>배포는 병합부터 자동으로 이어진다</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>&lt; 10초</t>
+          <t>CI 성공 후 자동 배포</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>비용</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>NFR-P-004</t>
+          <t>NFR-C-001</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>지침서 생성 시간</t>
+          <t>모델 호출 절감</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>모델 2회 호출로 지침서를 만드는 시간</t>
+          <t>같은 공고의 분석을 다시 쓰고, 재판정은 모델을 부르지 않는다</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>&lt; 60초</t>
+          <t>분석 결과 재사용</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>NFR-S-001</t>
+          <t>NFR-U-001</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>통신 암호화</t>
+          <t>모바일 대응</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>클라이언트-서버 간 통신 암호화</t>
+          <t>휴대폰 폭에서도 가로 스크롤 없이 쓸 수 있다</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Caddy 자동 HTTPS(TLS)</t>
+          <t>360 · 768 · 1440px E2E</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>NFR-S-002</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>회사 간 데이터 격리</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>다른 회사의 검토 건·프로필·판정에 접근할 수 없다</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>접근 시 403</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>NFR-S-003</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>비밀 정보 관리</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>API 키와 DB 비밀번호를 저장소·이미지에 두지 않는다</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>AWS SSM Parameter Store에서 실행 시 주입, GitHub는 OIDC 역할</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>NFR-S-004</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>비밀번호 저장</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>비밀번호와 세션 토큰을 원문으로 저장하지 않는다</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>PBKDF2-SHA256 21만 회, 세션은 SHA-256 해시</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>NFR-S-005</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>결제 정보 미수집</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>카드 정보를 받거나 저장하지 않는다</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>가입 API에 카드 필드 없음</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>NFR-S-006</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>외부 전달 동의</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>회사 정보가 외부 AI로 나가기 전에 동의를 받는다</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Copilot·지침서 동의 전 호출 불가</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>NFR-O-001</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>스키마 정합 배포</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>DB 스키마와 코드가 어긋나면 배포하지 않는다</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>스키마 검사 실패 시 이전 이미지로 복귀</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>NFR-O-002</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>자동 배포</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>병합부터 배포까지 사람 손 없이 이어진다</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>develop CI 성공 → AWS 자동 배포</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>NFR-O-003</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>배포 결과 확인</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>배포 명령의 실제 결과를 기다려 확인한다</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>SSM 명령 완료까지 대기(100초 타임아웃 제거)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>NFR-C-001</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>모델 호출 절감</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>같은 공고의 분석을 다시 쓰고 재판정은 모델을 부르지 않는다</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>분석 결과 재사용</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>NFR-C-002</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>사용량 한도</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>요금제별 한도로 모델 호출 비용을 제한한다</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>무료 계정 월 3건·공고당 질문 6회</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Must · BM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>사용성</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>NFR-U-001</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>모바일 대응</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>휴대폰 폭에서도 가로 스크롤 없이 쓸 수 있다</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>360 · 768 · 1440px E2E</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>사용성</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>NFR-U-002</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>키보드 조작</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>모든 검색을 Enter로 실행하고 주요 단추에 접근 가능한 이름을 붙인다</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>aria-label · Enter 제출</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>사용성</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>NFR-U-003</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>판정 결과 이해</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>확인 필요를 실패로 오해하지 않게 핵심 자격과 확인할 항목을 나눠 보여 준다</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>화면 분리 표시</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>유지보수성</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>NFR-M-001</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>CI 검사</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>PR마다 엔진·측정·백엔드·프론트·Django·통합 검사를 돌린다</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Actions 필수 검사</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>유지보수성</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>NFR-M-002</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>엔진 분리</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>엔진은 DB·API를 import하지 않는다</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>엔진 경계 테스트</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>유지보수성</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>NFR-M-003</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>영역 분리</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>PR이 어느 영역을 바꾸는지 알린다</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Zone guard</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>유지보수성</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>NFR-M-004</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>API 문서화</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>API 명세를 코드에서 자동 생성한다</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>FastAPI OpenAPI(/docs)</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Should</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>윤리·콘텐츠</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>NFR-E-001</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>판정 한계 고지</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>법적 참가 가능 여부를 보증하지 않고 최종 판단은 원문으로 하게 안내한다</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>화면·지침서 고지 문구</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>윤리·콘텐츠</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>NFR-E-002</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>점수 예측 금지</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>평가 점수나 낙찰 가능성을 예측하지 않는다</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Copilot·지침서 지시문에 명시</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>총 비기능 요구사항 건수: 30건</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>v1.0 (2026-10-14)</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>총 비기능 요구사항 건수: 11건</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>v1.1 (2026-10-15)</t>
         </is>
       </c>
     </row>
